--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N141_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N141_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.85572714610544</v>
+        <v>9.076555661242134</v>
       </c>
       <c r="D2" t="n">
-        <v>56.15267735475683</v>
+        <v>9.124810070147985</v>
       </c>
       <c r="E2" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F2" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.58426049032413</v>
+        <v>6.594942329677672</v>
       </c>
       <c r="D3" t="n">
-        <v>40.05113202036979</v>
+        <v>6.508308953310092</v>
       </c>
       <c r="E3" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F3" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.20094335453899</v>
+        <v>5.070153295112586</v>
       </c>
       <c r="D4" t="n">
-        <v>31.92616415610066</v>
+        <v>5.188001675366357</v>
       </c>
       <c r="E4" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F4" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.56591291470313</v>
+        <v>7.729460848639258</v>
       </c>
       <c r="D5" t="n">
-        <v>48.91660763535243</v>
+        <v>7.948948740744771</v>
       </c>
       <c r="E5" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F5" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.07357713769754</v>
+        <v>8.949456284875851</v>
       </c>
       <c r="D6" t="n">
-        <v>55.42855888730044</v>
+        <v>9.007140819186322</v>
       </c>
       <c r="E6" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F6" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>92.28866878231963</v>
+        <v>14.99690867712694</v>
       </c>
       <c r="D7" t="n">
-        <v>92.42896074230632</v>
+        <v>15.01970612062478</v>
       </c>
       <c r="E7" t="n">
-        <v>19.19832338475884</v>
+        <v>3.119727550023311</v>
       </c>
       <c r="F7" t="n">
-        <v>19.10928925806244</v>
+        <v>3.105259504435146</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
